--- a/docs/observable/kv-client-excel/kv-client-观测-调用链与URMA-TCP.xlsx
+++ b/docs/observable/kv-client-excel/kv-client-观测-调用链与URMA-TCP.xlsx
@@ -427,21 +427,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="64" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
     <col width="56" customWidth="1" min="8" max="8"/>
     <col width="56" customWidth="1" min="9" max="9"/>
     <col width="56" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="56" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,22 +485,12 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>详细故障原因解释</t>
+          <t>原因与定位建议</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>返回方式/重试策略</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>定位建议(简短)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>代码锚点</t>
+          <t>备注(返回/重试/代码锚点)</t>
         </is>
       </c>
     </row>
@@ -514,7 +502,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KVClient::Init (client本地访问)
+          <t>KVClient::Init (client组件)
   |_ ObjectClientImpl::Init
     |_ ValidateRequest(K_INVALID)
 [步骤] HostPort/凭证非法
@@ -557,22 +545,14 @@
         <is>
           <t>- 失败发生在 SDK 参数校验阶段
 - 请求未进入下游 worker/RPC
-- 常见根因: key/offset/timeout/batch 与接口约束不一致</t>
+- 常见根因: key/offset/timeout/batch 与接口约束不一致
+- 定位建议: 核对 IP/端口/AKSK 与部署一致</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>返回: 直接RETURN；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>核对 IP/端口/AKSK 与部署一致</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>object_client_impl.cpp Init</t>
+          <t>返回: 直接RETURN；重试: 通常不重试。
+- 代码锚点: object_client_impl.cpp Init</t>
         </is>
       </c>
     </row>
@@ -584,7 +564,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>InitClientWorkerConnect (worker1本地访问)
+          <t>InitClientWorkerConnect (worker组件)
   |_ Connect
     |_ RegisterClient
       |_ RPC调用
@@ -595,7 +575,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>RPC框架</t>
+          <t>OS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -637,22 +617,14 @@
         <is>
           <t>- 故障位于 RPC 传输层（ZMQ/TCP）或 OS 网络层
 - 常见表现: 连接不可达、poll超时、短暂不可用
-- 建议: 对齐 client/worker 同 key 时间线确认</t>
+- 建议: 对齐 client/worker 同 key 时间线确认
+- 定位建议: 查 worker 监听、防火墙、ZMQ 会话是否复用异常</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>返回: Status返回；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>查 worker 监听、防火墙、ZMQ 会话是否复用异常</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_common_api.cpp Connect</t>
+          <t>返回: Status返回；重试: 通常不重试。
+- 代码锚点: client_worker_common_api.cpp Connect</t>
         </is>
       </c>
     </row>
@@ -664,7 +636,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>InitClientWorkerConnect (worker1本地访问)
+          <t>InitClientWorkerConnect (worker组件)
   |_ Connect
     |_ RegisterClient
       |_ RPC调用
@@ -675,7 +647,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>OS+RPC框架</t>
+          <t>OS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -719,22 +691,14 @@
         <is>
           <t>- 故障位于 RPC 传输层（ZMQ/TCP）或 OS 网络层
 - 常见表现: 连接不可达、poll超时、短暂不可用
-- 建议: 对齐 client/worker 同 key 时间线确认</t>
+- 建议: 对齐 client/worker 同 key 时间线确认
+- 定位建议: 查 ZMQ HWM/超时参数、网络抖动、对端是否卡死</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>返回: 状态直接返回；重试: 连接阶段通常快速失败，业务RPC阶段按 RetryOnError 对 1001/1002/19 退避重试。</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>查 ZMQ HWM/超时参数、网络抖动、对端是否卡死</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_common_api.cpp; client_worker_remote_api.cpp</t>
+          <t>返回: 状态直接返回；重试: 连接阶段通常快速失败，业务RPC阶段按 RetryOnError 对 1001/1002/19 退避重试。
+- 代码锚点: client_worker_common_api.cpp; client_worker_remote_api.cpp</t>
         </is>
       </c>
     </row>
@@ -746,7 +710,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PostRegisterClient (client本地访问)
+          <t>PostRegisterClient (client组件)
   |_ FastTransportHandshake
     |_ UrmaInit
 [步骤] UB 握手 urma_init 等失败
@@ -756,7 +720,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>UMDK/URMA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -796,22 +760,14 @@
         <is>
           <t>- 故障位于 UB/URMA 数据面或连接状态机
 - 常见根因: 设备/驱动/UMDK、CQ 事件处理异常
-- 影响: 触发降级TCP或要求重连</t>
+- 影响: 触发降级TCP或要求重连
+- 定位建议: 查 UMDK、设备名、bonding、驱动</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>返回: LOG_IF_ERROR不阻断Init；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>查 UMDK、设备名、bonding、驱动</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>urma_manager.cpp UrmaInit</t>
+          <t>返回: LOG_IF_ERROR不阻断Init；重试: 通常不重试。
+- 代码锚点: urma_manager.cpp UrmaInit</t>
         </is>
       </c>
     </row>
@@ -823,7 +779,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PostRegisterClient (client本地访问)
+          <t>PostRegisterClient (client组件)
   |_ InitMemoryBufferPool
 [步骤] UB 客户端池 mmap 失败
 [发生位置] client1
@@ -872,22 +828,14 @@
         <is>
           <t>- 故障位于 OS 资源层（fd/内存映射）
 - 常见根因: fd 传递时序异常、权限/上限不足
-- 建议: 联查 ulimit、vm.max_map_count、进程fd占用</t>
+- 建议: 联查 ulimit、vm.max_map_count、进程fd占用
+- 定位建议: 查进程内存限制、vm.max_map_count、ulimit</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>返回: 链上RETURN；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>查进程内存限制、vm.max_map_count、ulimit</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>urma_manager.cpp InitMemoryBufferPool</t>
+          <t>返回: 链上RETURN；重试: 通常不重试。
+- 代码锚点: urma_manager.cpp InitMemoryBufferPool</t>
         </is>
       </c>
     </row>
@@ -899,7 +847,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>PostRegisterClient (worker1本地访问)
+          <t>PostRegisterClient (worker组件)
   |_ ExchangeJfr
     |_ ImportRemoteJfr
 [步骤] ExchangeJfr/import 失败
@@ -909,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>UMDK/URMA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -948,22 +896,14 @@
         <is>
           <t>- 故障位于 UB/URMA 数据面或连接状态机
 - 常见根因: 设备/驱动/UMDK、CQ 事件处理异常
-- 影响: 触发降级TCP或要求重连</t>
+- 影响: 触发降级TCP或要求重连
+- 定位建议: 查 client-worker UB 握手、对端 jfr 可达性</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>返回: 仅ERROR日志；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>查 client-worker UB 握手、对端 jfr 可达性</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>urma_manager.cpp ExchangeJfr</t>
+          <t>返回: 仅ERROR日志；重试: 通常不重试。
+- 代码锚点: urma_manager.cpp ExchangeJfr</t>
         </is>
       </c>
     </row>
@@ -975,7 +915,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PostRegisterClient (client本地访问)
+          <t>PostRegisterClient (client组件)
   |_ RecvPageFd
     |_ SockRecvFd
 [步骤] UDS 收 fd 失败
@@ -1026,22 +966,14 @@
         <is>
           <t>- 故障位于 OS 资源层（fd/内存映射）
 - 常见根因: fd 传递时序异常、权限/上限不足
-- 建议: 联查 ulimit、vm.max_map_count、进程fd占用</t>
+- 建议: 联查 ulimit、vm.max_map_count、进程fd占用
+- 定位建议: 查 UDS 路径、fd 上限、对端是否先发 fd</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>返回: 线程内失败；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>查 UDS 路径、fd 上限、对端是否先发 fd</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>fd_pass.cpp SockRecvFd</t>
+          <t>返回: 线程内失败；重试: 通常不重试。
+- 代码锚点: fd_pass.cpp SockRecvFd</t>
         </is>
       </c>
     </row>
@@ -1053,7 +985,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ObjectClientImpl::Get (client本地访问)
+          <t>ObjectClientImpl::Get (client组件)
   |_ ClientWorkerRemoteApi::Get
     |_ PreGet
       |_ ValidateRequest(K_INVALID)
@@ -1098,22 +1030,14 @@
         <is>
           <t>- 失败发生在 SDK 参数校验阶段
 - 请求未进入下游 worker/RPC
-- 常见根因: key/offset/timeout/batch 与接口约束不一致</t>
+- 常见根因: key/offset/timeout/batch 与接口约束不一致
+- 定位建议: 核对 SDK 入参与 OBJECT_KEYS_MAX_LIMIT</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>返回: 直接RETURN；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>核对 SDK 入参与 OBJECT_KEYS_MAX_LIMIT</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_base_api.cpp PreGet</t>
+          <t>返回: 直接RETURN；重试: 通常不重试。
+- 代码锚点: client_worker_base_api.cpp PreGet</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1049,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ClientWorkerRemoteApi::Get (client本地访问)
+          <t>ClientWorkerRemoteApi::Get (client组件)
   |_ PrepareUrmaBuffer
 [步骤] UB 缓冲准备失败降级
 [发生位置] client1
@@ -1134,7 +1058,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>URMA(可降级)</t>
+          <t>UMDK/URMA</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1145,7 +1069,8 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>（补充）URMA链路调用
+见调用链中的 urma_* / jfc / jfr / jfs</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1172,22 +1097,14 @@
         <is>
           <t>- 故障位于 UB/URMA 数据面或连接状态机
 - 常见根因: 设备/驱动/UMDK、CQ 事件处理异常
-- 影响: 触发降级TCP或要求重连</t>
+- 影响: 触发降级TCP或要求重连
+- 定位建议: 功能可成功；性能差则查 UB 池初始化与并发</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>返回: 不返回URMA码继续RPC；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>功能可成功；性能差则查 UB 池初始化与并发</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_base_api.cpp PrepareUrmaBuffer</t>
+          <t>返回: 不返回URMA码继续RPC；重试: 通常不重试。
+- 代码锚点: client_worker_base_api.cpp PrepareUrmaBuffer</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1116,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ClientWorkerRemoteApi::Get (worker1本地访问)
+          <t>ClientWorkerRemoteApi::Get (worker组件)
   |_ RetryOnError
     |_ stub_-&gt;Get
 [步骤] 控制面 RPC 失败/重试耗尽
@@ -1209,7 +1126,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>RPC框架</t>
+          <t>OS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1252,22 +1169,14 @@
         <is>
           <t>- 故障位于 RPC 传输层（ZMQ/TCP）或 OS 网络层
 - 常见表现: 连接不可达、poll超时、短暂不可用
-- 建议: 对齐 client/worker 同 key 时间线确认</t>
+- 建议: 对齐 client/worker 同 key 时间线确认
+- 定位建议: 无 worker 入口日志→网络；有入口→worker 慢或下游</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>返回: Status返回；重试: RetryOnError。</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>无 worker 入口日志→网络；有入口→worker 慢或下游</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_remote_api.cpp Get</t>
+          <t>返回: Status返回；重试: RetryOnError。
+- 代码锚点: client_worker_remote_api.cpp Get</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1188,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ClientWorkerRemoteApi::Get (worker1本地访问)
+          <t>ClientWorkerRemoteApi::Get (worker组件)
   |_ RetryOnError
     |_ stub_-&gt;Get
 [步骤] RPC socket 读写失败/超时
@@ -1289,7 +1198,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>OS+RPC框架</t>
+          <t>OS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1333,22 +1242,14 @@
         <is>
           <t>- 故障位于 RPC 传输层（ZMQ/TCP）或 OS 网络层
 - 常见表现: 连接不可达、poll超时、短暂不可用
-- 建议: 对齐 client/worker 同 key 时间线确认</t>
+- 建议: 对齐 client/worker 同 key 时间线确认
+- 定位建议: 抓包+对齐 SDK/worker 同 key 时间线</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>返回: 重试后返回；重试: RetryOnError。</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>抓包+对齐 SDK/worker 同 key 时间线</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_remote_api.cpp</t>
+          <t>返回: 重试后返回；重试: RetryOnError。
+- 代码锚点: client_worker_remote_api.cpp</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1261,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Get lambda (worker1本地访问)
+          <t>Get lambda (worker组件)
   |_ last_rc 评估
     |_ RPC调用
 [步骤] 业务 last_rc 超时/OOM 触发重试
@@ -1370,7 +1271,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>数据系统逻辑</t>
+          <t>数据系统</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1393,7 +1294,8 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>（补充）OS/RPC调用
+socket/connect/send/recv/zmq_poll/mmap/fd</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1412,22 +1314,14 @@
         <is>
           <t>- 故障位于 RPC 传输层（ZMQ/TCP）或 OS 网络层
 - 常见表现: 连接不可达、poll超时、短暂不可用
-- 建议: 对齐 client/worker 同 key 时间线确认</t>
+- 建议: 对齐 client/worker 同 key 时间线确认
+- 定位建议: 查 worker 负载、远端拉取、内存</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>返回: 重试；重试: 见RPC。</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>查 worker 负载、远端拉取、内存</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_remote_api.cpp Get lambda</t>
+          <t>返回: 重试；重试: 见RPC。
+- 代码锚点: client_worker_remote_api.cpp Get lambda</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1333,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ProcessGetObjectRequest (worker1本地访问)
+          <t>ProcessGetObjectRequest (worker组件)
   |_ QueryMeta
 [步骤] etcd 续约不可用
 [发生位置] worker1
@@ -1448,7 +1342,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>数据系统逻辑</t>
+          <t>数据系统</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1469,7 +1363,8 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>（补充）OS/RPC调用
+socket/connect/send/recv/zmq_poll/mmap/fd</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1488,22 +1383,14 @@
         <is>
           <t>- 故障位于 RPC 传输层（ZMQ/TCP）或 OS 网络层
 - 常见表现: 连接不可达、poll超时、短暂不可用
-- 建议: 对齐 client/worker 同 key 时间线确认</t>
+- 建议: 对齐 client/worker 同 key 时间线确认
+- 定位建议: 查 etcd 集群与 worker 续约</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>返回: last_rc；重试: worker内策略。</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>查 etcd 集群与 worker 续约</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>worker_oc_service_get_impl.cpp</t>
+          <t>返回: last_rc；重试: worker内策略。
+- 代码锚点: worker_oc_service_get_impl.cpp</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1402,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ProcessGetObjectRequest (worker2元数据)
+          <t>ProcessGetObjectRequest (worker-元数据访问)
   |_ QueryMeta
 [步骤] QueryMeta/Master 失败
 [发生位置] worker1-&gt;worker2
@@ -1524,7 +1411,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>数据系统逻辑+RPC</t>
+          <t>RPC框架</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1557,22 +1444,14 @@
         <is>
           <t>- 故障位于数据系统业务链路（元数据/远端拉取/副本）
 - 非单纯 URMA/OS 根因
-- 建议: 沿 worker1-&gt;worker2/worker3 逐段排查</t>
+- 建议: 沿 worker1-&gt;worker2/worker3 逐段排查
+- 定位建议: 查 Master 可用性与元数据一致性</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>返回: last_rc；重试: 视实现。</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>查 Master 可用性与元数据一致性</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>worker_oc_service_get_impl.cpp</t>
+          <t>返回: last_rc；重试: 视实现。
+- 代码锚点: worker_oc_service_get_impl.cpp</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1463,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ProcessGetObjectRequest (worker3数据)
+          <t>ProcessGetObjectRequest (worker-数据拉取)
   |_ GetObjectFromRemote
 [步骤] 远端 Worker 拉取失败
 [发生位置] worker1-&gt;worker3
@@ -1593,7 +1472,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>数据系统逻辑+RPC</t>
+          <t>RPC框架</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1614,7 +1493,8 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>（补充）OS/RPC调用
+socket/connect/send/recv/zmq_poll/mmap/fd</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1633,22 +1513,14 @@
         <is>
           <t>- 故障位于 RPC 传输层（ZMQ/TCP）或 OS 网络层
 - 常见表现: 连接不可达、poll超时、短暂不可用
-- 建议: 对齐 client/worker 同 key 时间线确认</t>
+- 建议: 对齐 client/worker 同 key 时间线确认
+- 定位建议: 对齐 worker3 日志与同 key</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>返回: last_rc/RPC；重试: TryReconnect…。</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>对齐 worker3 日志与同 key</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>worker_oc_service_get_impl.cpp</t>
+          <t>返回: last_rc/RPC；重试: TryReconnect…。
+- 代码锚点: worker_oc_service_get_impl.cpp</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1532,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>UrmaWritePayload (worker3数据)
+          <t>UrmaWritePayload (worker-数据拉取)
   |_ urma_write/read
 [步骤] URMA write/read 失败
 [发生位置] worker3
@@ -1669,7 +1541,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>UMDK/URMA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1708,22 +1580,14 @@
         <is>
           <t>- 故障位于 UB/URMA 数据面或连接状态机
 - 常见根因: 设备/驱动/UMDK、CQ 事件处理异常
-- 影响: 触发降级TCP或要求重连</t>
+- 影响: 触发降级TCP或要求重连
+- 定位建议: 查对端可达、完成错误、UMDK 日志</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>返回: 汇总回 client；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>查对端可达、完成错误、UMDK 日志</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>urma_manager.cpp</t>
+          <t>返回: 汇总回 client；重试: 通常不重试。
+- 代码锚点: urma_manager.cpp</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1599,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PollJfcWait (worker3数据)
+          <t>PollJfcWait (worker-数据拉取)
   |_ urma_wait/poll/rearm_jfc
 [步骤] URMA poll/wait jfc 失败
 [发生位置] worker3
@@ -1744,7 +1608,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>UMDK/URMA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1772,7 +1636,8 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>（补充）OS/RPC调用
+socket/connect/send/recv/zmq_poll/mmap/fd</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1791,22 +1656,14 @@
         <is>
           <t>- 故障位于 UB/URMA 数据面或连接状态机
 - 常见根因: 设备/驱动/UMDK、CQ 事件处理异常
-- 影响: 触发降级TCP或要求重连</t>
+- 影响: 触发降级TCP或要求重连
+- 定位建议: 查 CQ、事件模式、设备状态</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>返回: 汇总回 client；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>查 CQ、事件模式、设备状态</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>urma_manager.cpp PollJfcWait</t>
+          <t>返回: 汇总回 client；重试: 通常不重试。
+- 代码锚点: urma_manager.cpp PollJfcWait</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1675,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CheckUrmaConnectionStable (worker3数据)
+          <t>CheckUrmaConnectionStable (worker-数据拉取)
 [步骤] URMA 需重连
 [发生位置] worker1/worker3
 [详细描述] 入口或数据面连通性检测</t>
@@ -1826,7 +1683,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>UMDK/URMA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1864,22 +1721,14 @@
         <is>
           <t>- 故障位于 UB/URMA 数据面或连接状态机
 - 常见根因: 设备/驱动/UMDK、CQ 事件处理异常
-- 影响: 触发降级TCP或要求重连</t>
+- 影响: 触发降级TCP或要求重连
+- 定位建议: 重建 UB 会话后再试</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>返回: Status；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>重建 UB 会话后再试</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>urma_manager.cpp</t>
+          <t>返回: Status；重试: 通常不重试。
+- 代码锚点: urma_manager.cpp</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1740,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FillUrmaBuffer (client本地访问)
+          <t>FillUrmaBuffer (client组件)
   |_ GetBuffersFromWorker
 [步骤] FillUrmaBuffer 越界/组装失败
 [发生位置] client1
@@ -1900,7 +1749,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>数据系统逻辑</t>
+          <t>UMDK/URMA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1933,22 +1782,14 @@
         <is>
           <t>- 可能由多层共同触发
 - 建议先按调用链分段(client1/worker1/worker2/worker3)
-- 再结合状态码与日志关键词交叉定界</t>
+- 再结合状态码与日志关键词交叉定界
+- 定位建议: 查 worker 返回的 payload 与 UB 尺寸一致性</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>返回: 直接RETURN；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>查 worker 返回的 payload 与 UB 尺寸一致性</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_base_api.cpp FillUrmaBuffer</t>
+          <t>返回: 直接RETURN；重试: 通常不重试。
+- 代码锚点: client_worker_base_api.cpp FillUrmaBuffer</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1801,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MmapShmUnit (client本地访问)
+          <t>MmapShmUnit (client组件)
   |_ LookupUnitsAndMmapFd
 [步骤] SHM mmap 失败
 [发生位置] client1
@@ -1969,7 +1810,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>OS+数据系统</t>
+          <t>OS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2009,22 +1850,14 @@
         <is>
           <t>- 故障位于 OS 资源层（fd/内存映射）
 - 常见根因: fd 传递时序异常、权限/上限不足
-- 建议: 联查 ulimit、vm.max_map_count、进程fd占用</t>
+- 建议: 联查 ulimit、vm.max_map_count、进程fd占用
+- 定位建议: 查 fd 是否有效、是否同机、表项是否注册</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>返回: 单key失败聚合；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>查 fd 是否有效、是否同机、表项是否注册</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>object_client_impl.cpp MmapShmUnit</t>
+          <t>返回: 单key失败聚合；重试: 通常不重试。
+- 代码锚点: object_client_impl.cpp MmapShmUnit</t>
         </is>
       </c>
     </row>
@@ -2036,7 +1869,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ProcessGetObjectRequest (worker3数据)
+          <t>ProcessGetObjectRequest (worker-数据拉取)
 [步骤] K_NOT_FOUND 对象不存在
 [发生位置] worker1/worker3
 [详细描述] 入口到数据副本</t>
@@ -2044,7 +1877,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>数据系统逻辑</t>
+          <t>数据系统</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2077,22 +1910,14 @@
         <is>
           <t>- 故障位于数据系统业务链路（元数据/远端拉取/副本）
 - 非单纯 URMA/OS 根因
-- 建议: 沿 worker1-&gt;worker2/worker3 逐段排查</t>
+- 建议: 沿 worker1-&gt;worker2/worker3 逐段排查
+- 定位建议: 数据/副本/过期，非 URMA/OS 根因</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>返回: last_rc；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>数据/副本/过期，非 URMA/OS 根因</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>worker_oc_service_get_impl.cpp</t>
+          <t>返回: last_rc；重试: 通常不重试。
+- 代码锚点: worker_oc_service_get_impl.cpp</t>
         </is>
       </c>
     </row>
@@ -2104,7 +1929,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SendBufferViaUb (client本地访问)
+          <t>SendBufferViaUb (client组件)
   |_ UrmaWritePayload
 [步骤] UB 单对象发送失败
 [发生位置] client1
@@ -2113,7 +1938,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>URMA</t>
+          <t>UMDK/URMA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2152,22 +1977,14 @@
         <is>
           <t>- 故障位于 UB/URMA 数据面或连接状态机
 - 常见根因: 设备/驱动/UMDK、CQ 事件处理异常
-- 影响: 触发降级TCP或要求重连</t>
+- 影响: 触发降级TCP或要求重连
+- 定位建议: 查 UB 池大小与对象总大小</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>返回: 可改走非UB；重试: 通常不重试。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>查 UB 池大小与对象总大小</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_base_api.cpp SendBufferViaUb</t>
+          <t>返回: 可改走非UB；重试: 通常不重试。
+- 代码锚点: client_worker_base_api.cpp SendBufferViaUb</t>
         </is>
       </c>
     </row>
@@ -2179,7 +1996,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Publish (worker1本地访问)
+          <t>Publish (worker组件)
   |_ RetryOnError
     |_ stub_-&gt;Publish
 [步骤] Publish RPC 失败
@@ -2189,7 +2006,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>RPC框架</t>
+          <t>OS</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2232,22 +2049,14 @@
         <is>
           <t>- 故障位于 RPC 传输层（ZMQ/TCP）或 OS 网络层
 - 常见表现: 连接不可达、poll超时、短暂不可用
-- 建议: 对齐 client/worker 同 key 时间线确认</t>
+- 建议: 对齐 client/worker 同 key 时间线确认
+- 定位建议: 同 Get 控制面</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>返回: Status；重试: RetryOnError。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>同 Get 控制面</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_remote_api.cpp Publish</t>
+          <t>返回: Status；重试: RetryOnError。
+- 代码锚点: client_worker_remote_api.cpp Publish</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2068,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Publish/MultiPublish RPC (worker1本地访问)
+          <t>Publish/MultiPublish RPC (worker组件)
   |_ RPC调用
 [步骤] Publish/MultiPublish socket 读写失败/超时
 [发生位置] client1-&gt;worker1
@@ -2268,7 +2077,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>OS+RPC框架</t>
+          <t>OS</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2312,22 +2121,14 @@
         <is>
           <t>- 故障位于 RPC 传输层（ZMQ/TCP）或 OS 网络层
 - 常见表现: 连接不可达、poll超时、短暂不可用
-- 建议: 对齐 client/worker 同 key 时间线确认</t>
+- 建议: 对齐 client/worker 同 key 时间线确认
+- 定位建议: 查 ZMQ 超时与水位，关注队列堆积</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>返回: 重试后返回；重试: RetryOnError。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>查 ZMQ 超时与水位，关注队列堆积</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_remote_api.cpp</t>
+          <t>返回: 重试后返回；重试: RetryOnError。
+- 代码锚点: client_worker_remote_api.cpp</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2140,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MultiPublish (worker1本地访问)
+          <t>MultiPublish (worker组件)
   |_ RetryOnError
 [步骤] MultiPublish 扩缩容/内存
 [发生位置] client1-&gt;worker1
@@ -2348,7 +2149,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>数据系统逻辑</t>
+          <t>数据系统</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2382,22 +2183,14 @@
         <is>
           <t>- 可能由多层共同触发
 - 建议先按调用链分段(client1/worker1/worker2/worker3)
-- 再结合状态码与日志关键词交叉定界</t>
+- 再结合状态码与日志关键词交叉定界
+- 定位建议: 查集群 scaling 状态与批次大小</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>返回: Status；重试: RetryOnError含扩展码。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>查集群 scaling 状态与批次大小</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>client_worker_remote_api.cpp MultiPublish</t>
+          <t>返回: Status；重试: RetryOnError含扩展码。
+- 代码锚点: client_worker_remote_api.cpp MultiPublish</t>
         </is>
       </c>
     </row>
